--- a/reports/一级子公司A_利润表_2025-11.xlsx
+++ b/reports/一级子公司A_利润表_2025-11.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>166166102</v>
+        <v>169427903</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>161915669</v>
+        <v>161452249</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1856491702</v>
+        <v>1855667461</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>656744</v>
+        <v>662894</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7567667</v>
+        <v>7569197</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>571263</v>
+        <v>575319</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>6565607</v>
+        <v>6570132</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>482360</v>
+        <v>487259</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5560937</v>
+        <v>5569726</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>446174</v>
+        <v>447653</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5117243</v>
+        <v>5125083</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>241683</v>
+        <v>242791</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2779945</v>
+        <v>2785379</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>194480</v>
+        <v>193802</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2225057</v>
+        <v>2227902</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>163573398</v>
+        <v>166818185</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>159322965</v>
+        <v>158842531</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82424196</v>
+        <v>81533528</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>940760713</v>
+        <v>940505288</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1509551</v>
+        <v>1495306</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>17261062</v>
+        <v>17241329</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1363887</v>
+        <v>1352835</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>15593568</v>
+        <v>15566669</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>72397551</v>
+        <v>72819265</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>834448172</v>
+        <v>833938668</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1558974</v>
+        <v>1555188</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>17819649</v>
+        <v>17794790</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>676065</v>
+        <v>681083</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>7791456</v>
+        <v>7786953</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2433260</v>
+        <v>2437877</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>27837924</v>
+        <v>27829497</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1061736</v>
+        <v>1072473</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>12240220</v>
+        <v>12245596</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4160717</v>
+        <v>4192801</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>47847901</v>
+        <v>47886946</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89716</v>
+        <v>90392</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>989362</v>
+        <v>991019</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2217342</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>25403003</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1475119</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>16934350</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>110859612</v>
+        <v>118334461</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>99029306</v>
+        <v>98553492</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>96980503</v>
+        <v>96527248</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1112650095</v>
+        <v>1112944523</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2048803</v>
+        <v>2026244</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>23383009</v>
+        <v>23363087</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3668513</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>42259559</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1175524</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>13520334</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>736142</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>8450019</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>885321</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>10141646</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>665364</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>7608632</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>444271</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5074523</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>370518</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4230630</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1687363</v>
+        <v>1706092</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>19466255</v>
+        <v>19490933</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1309653</v>
+        <v>1314786</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>15021440</v>
+        <v>15039811</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1062645</v>
+        <v>1069598</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>12232623</v>
+        <v>12255873</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8059077</v>
+        <v>8053282</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>92335052</v>
+        <v>92469184</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>350041</v>
+        <v>338907</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3847500</v>
+        <v>3898437</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>671180</v>
+        <v>667437</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>7367909</v>
+        <v>7372365</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>762962</v>
+        <v>667437</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>8360655</v>
+        <v>7372365</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90138</v>
+        <v>89526</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>990148</v>
+        <v>989419</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>340424</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>3758353</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>643014</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>7393832</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>227738</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2505179</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>171182</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1879299</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>285879</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3133356</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>925706</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>10572540</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152797</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1672720</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114569</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1255046</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>190736</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2092286</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>133275</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1464699</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>94990</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1046068</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>75829</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>836588</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56772</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>627167</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>52713786</v>
+        <v>50775139</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>61122525</v>
+        <v>56837697</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>366957</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4225662</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>94724</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1043790</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>149930</v>
+        <v>149865</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1650962</v>
+        <v>1648167</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>52563856</v>
+        <v>50992231</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5277349</v>
+        <v>5317549</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>58307926</v>
+        <v>58272780</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>47286507</v>
+        <v>45674682</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>47286507</v>
+        <v>45674682</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>47286507</v>
+        <v>45674682</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>47286507</v>
+        <v>45674682</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>47286507</v>
+        <v>45674682</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
